--- a/artfynd/A 41542-2022 artfynd.xlsx
+++ b/artfynd/A 41542-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41542-2022 artfynd.xlsx
+++ b/artfynd/A 41542-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1566,6 +1566,117 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128785827</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58547</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100117</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Långbensgroda</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rana dalmatina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bonaparte, 1840</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Motorpet 2, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>567343</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6263228</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Halltorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eike Amthauer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eike Amthauer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41542-2022 artfynd.xlsx
+++ b/artfynd/A 41542-2022 artfynd.xlsx
@@ -1571,7 +1571,7 @@
         <v>128785827</v>
       </c>
       <c r="B9" t="n">
-        <v>58547</v>
+        <v>58574</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41542-2022 artfynd.xlsx
+++ b/artfynd/A 41542-2022 artfynd.xlsx
@@ -1571,7 +1571,7 @@
         <v>128785827</v>
       </c>
       <c r="B9" t="n">
-        <v>58574</v>
+        <v>58578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41542-2022 artfynd.xlsx
+++ b/artfynd/A 41542-2022 artfynd.xlsx
@@ -1571,7 +1571,7 @@
         <v>128785827</v>
       </c>
       <c r="B9" t="n">
-        <v>58578</v>
+        <v>58581</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41542-2022 artfynd.xlsx
+++ b/artfynd/A 41542-2022 artfynd.xlsx
@@ -1571,7 +1571,7 @@
         <v>128785827</v>
       </c>
       <c r="B9" t="n">
-        <v>58581</v>
+        <v>58583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41542-2022 artfynd.xlsx
+++ b/artfynd/A 41542-2022 artfynd.xlsx
@@ -1571,7 +1571,7 @@
         <v>128785827</v>
       </c>
       <c r="B9" t="n">
-        <v>58583</v>
+        <v>58585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41542-2022 artfynd.xlsx
+++ b/artfynd/A 41542-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3028617</v>
+        <v>128785827</v>
       </c>
       <c r="B2" t="n">
-        <v>96333</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100117</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana dalmatina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Bonaparte, 1840</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Motorpet 400 m S, Sm</t>
+          <t>Motorpet 2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567278.6810728589</v>
+        <v>567343</v>
       </c>
       <c r="R2" t="n">
-        <v>6262980.191433484</v>
+        <v>6263228</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-03-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-03-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,23 +767,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>tallskog, bland blåbärsris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Burén</t>
+          <t>Eike Amthauer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Burén</t>
+          <t>Eike Amthauer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -804,12 +789,7 @@
         <v>3028616</v>
       </c>
       <c r="B3" t="n">
-        <v>96333</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567491.754988055</v>
+        <v>567492</v>
       </c>
       <c r="R3" t="n">
-        <v>6262692.736509058</v>
+        <v>6262693</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -883,19 +863,9 @@
           <t>2009-03-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-03-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,70 +897,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96040931</v>
+        <v>3028617</v>
       </c>
       <c r="B4" t="n">
-        <v>57140</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100088</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Motorpet, Sm</t>
+          <t>Motorpet 400 m S, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567458.7132678726</v>
+        <v>567279</v>
       </c>
       <c r="R4" t="n">
-        <v>6263377.084020479</v>
+        <v>6262980</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,22 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-03-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-03-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,85 +985,83 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>tallskog, bland blåbärsris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eike Amthauer</t>
+          <t>Tomas Burén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eike Amthauer</t>
+          <t>Tomas Burén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96040936</v>
+        <v>97225716</v>
       </c>
       <c r="B5" t="n">
-        <v>55392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208257</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Motorpet, Sm</t>
+          <t>Namnerum 10:1, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567458.7132678726</v>
+        <v>567462</v>
       </c>
       <c r="R5" t="n">
-        <v>6263377.084020479</v>
+        <v>6262691</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1140,22 +1085,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>återfynd, senast rapporterad 2009</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,27 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eike Amthauer</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eike Amthauer</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97225716</v>
+        <v>97225723</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1153,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1235,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567461.9154569793</v>
+        <v>567488</v>
       </c>
       <c r="R6" t="n">
-        <v>6262691.156509344</v>
+        <v>6262702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,24 +1203,14 @@
           <t>2021-11-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-11-18</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>återfynd, senast rapporterad 2009</t>
+          <t>återfynd. senast rapporterad 2009</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,12 +1241,7 @@
         <v>97225726</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567548.7279094096</v>
+        <v>567549</v>
       </c>
       <c r="R7" t="n">
-        <v>6262865.289285505</v>
+        <v>6262865</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1398,19 +1318,9 @@
           <t>2021-11-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-11-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1435,247 +1345,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>97225723</v>
-      </c>
-      <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Namnerum 10:1, Sm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>567487.726103027</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6262702.606715872</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Halltorp</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2021-11-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2021-11-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>återfynd. senast rapporterad 2009</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>128785827</v>
-      </c>
-      <c r="B9" t="n">
-        <v>58585</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100117</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Långbensgroda</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Rana dalmatina</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Bonaparte, 1840</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Motorpet 2, Sm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>567343</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6263228</v>
-      </c>
-      <c r="S9" t="n">
-        <v>50</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Halltorp</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Eike Amthauer</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Eike Amthauer</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41542-2022 artfynd.xlsx
+++ b/artfynd/A 41542-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128785827</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3028616</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3028617</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97225716</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97225723</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,8 +1375,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97225726</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>